--- a/df_out.xlsx
+++ b/df_out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C316"/>
+  <dimension ref="A1:C342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>verdict</t>
+          <t>Verdict</t>
         </is>
       </c>
     </row>
@@ -5536,12 +5536,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>B0122001sc</t>
+          <t>B0205003p</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>B0387002sc</t>
+          <t>S0020927007p</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>B0108004p</t>
+          <t>B0247001p</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>B0196005p</t>
+          <t>B0247003p</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -5570,12 +5570,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>B0305004p</t>
+          <t>B0246002p</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>B0513006p</t>
+          <t>B0361004p</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -5587,12 +5587,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>B0713007p</t>
+          <t>B0208011p</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>S0020686007p</t>
+          <t>B0659003p</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -5604,12 +5604,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>B0138004p</t>
+          <t>B0125006p</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>B0195003p</t>
+          <t>B0230007p</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -5621,12 +5621,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>B0614003p</t>
+          <t>B0138008p</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>B0804006p</t>
+          <t>B0783009p</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -5638,12 +5638,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>B0286001sc</t>
+          <t>B0252005p</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>B0754002sc</t>
+          <t>B0800006p</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -5655,12 +5655,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>B0512002sc</t>
+          <t>B0108007p</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>B0663003sc</t>
+          <t>B0138006p</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>B0206003sc</t>
+          <t>B0133004p</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>B1160001sc</t>
+          <t>B0230010p</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>B0179001sc</t>
+          <t>B0194008p</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>B0250002sc</t>
+          <t>B0291010p</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -5706,12 +5706,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>B0937003sc</t>
+          <t>B0169001p</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>B0951001sc</t>
+          <t>B0345008p</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -5723,12 +5723,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>B0169006p</t>
+          <t>B0570001p</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>B0752001p</t>
+          <t>B0578004p</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -5740,12 +5740,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>B0345005p</t>
+          <t>B0166005p</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>B0800009p</t>
+          <t>B0295005p</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -5757,12 +5757,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>B0109009p</t>
+          <t>B0093002p</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>B0695004p</t>
+          <t>B0525009p</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -5774,15 +5774,457 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>B0159002p</t>
+          <t>B0217007p</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>S0024095006p</t>
+          <t>B0508001p</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>B0110003p</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>B0164003p</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>B0761005p</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>B0971007p</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>B0141011p</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>B0244009p</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>B0133001p</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>B0259003p</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>B0214001p</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>B0383004p</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>B0116003p</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>B0269009p</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>B0096005p</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>B0254005p</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>B0038007p</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>B0082005p</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>B0305004p</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>B0311003p</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>B0364009p</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>B0776004p</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>B0121009p</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>B0750005p</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>B0734006p</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>B0747002p</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>B0082003p</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>B0083004p</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>B0030005p</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>B0256001p</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>B0020004p</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>B0127002p</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>B0325008p</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>B0650001p</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>B0194004p</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>S0023860010p</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>B0079001p</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>B0190001p</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>B0344008p</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>B0345001p</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>B0210004p</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>B0677002p</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>B0030008p</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>B0231006p</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>B1045007p</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>B1101003p</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>B0106002p</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>B0364009p</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>B0253001p</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>B0348002p</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>B0190002p</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>B0505004p</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>B0035002p</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>B0769006p</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
